--- a/output/dataverse/Supplementary_Table_2_OPT.xlsx
+++ b/output/dataverse/Supplementary_Table_2_OPT.xlsx
@@ -386,10 +386,10 @@
         <v>7575436</v>
       </c>
       <c r="C2">
-        <v>138.77</v>
+        <v>137.22</v>
       </c>
       <c r="D2">
-        <v>33.71</v>
+        <v>34.34</v>
       </c>
     </row>
     <row r="3">
@@ -402,10 +402,10 @@
         <v>2307038</v>
       </c>
       <c r="C3">
-        <v>153.29</v>
+        <v>151.68</v>
       </c>
       <c r="D3">
-        <v>27.2</v>
+        <v>27.89</v>
       </c>
     </row>
     <row r="4">
@@ -418,10 +418,10 @@
         <v>912942</v>
       </c>
       <c r="C4">
-        <v>149.16</v>
+        <v>147.16</v>
       </c>
       <c r="D4">
-        <v>23.24</v>
+        <v>24.85</v>
       </c>
     </row>
     <row r="5">
@@ -434,10 +434,10 @@
         <v>624656</v>
       </c>
       <c r="C5">
-        <v>158.29</v>
+        <v>156.23</v>
       </c>
       <c r="D5">
-        <v>30.44</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="6">
@@ -450,10 +450,10 @@
         <v>460509</v>
       </c>
       <c r="C6">
-        <v>154.41</v>
+        <v>152.88</v>
       </c>
       <c r="D6">
-        <v>21.17</v>
+        <v>21.54</v>
       </c>
     </row>
     <row r="7">
@@ -466,10 +466,10 @@
         <v>369802</v>
       </c>
       <c r="C7">
-        <v>141.23</v>
+        <v>139.45</v>
       </c>
       <c r="D7">
-        <v>26.14</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="8">
@@ -482,10 +482,10 @@
         <v>1828298</v>
       </c>
       <c r="C8">
-        <v>106.28</v>
+        <v>105.26</v>
       </c>
       <c r="D8">
-        <v>51.75</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="9">
@@ -498,10 +498,10 @@
         <v>1072189</v>
       </c>
       <c r="C9">
-        <v>135.17</v>
+        <v>133.58</v>
       </c>
       <c r="D9">
-        <v>35.8</v>
+        <v>36.25</v>
       </c>
     </row>
     <row r="10">
@@ -514,10 +514,10 @@
         <v>35957</v>
       </c>
       <c r="C10">
-        <v>146.29</v>
+        <v>144.33</v>
       </c>
       <c r="D10">
-        <v>18.85</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="11">
@@ -530,10 +530,10 @@
         <v>2861</v>
       </c>
       <c r="C11">
-        <v>131.75</v>
+        <v>130.25</v>
       </c>
       <c r="D11">
-        <v>33.22</v>
+        <v>34.17</v>
       </c>
     </row>
     <row r="12">
@@ -546,10 +546,10 @@
         <v>41899</v>
       </c>
       <c r="C12">
-        <v>163.12</v>
+        <v>161.37</v>
       </c>
       <c r="D12">
-        <v>12.15</v>
+        <v>12.55</v>
       </c>
     </row>
     <row r="13">
@@ -562,10 +562,10 @@
         <v>30630</v>
       </c>
       <c r="C13">
-        <v>97.08</v>
+        <v>95.83</v>
       </c>
       <c r="D13">
-        <v>60.49</v>
+        <v>61.1</v>
       </c>
     </row>
     <row r="14">
@@ -578,10 +578,10 @@
         <v>90</v>
       </c>
       <c r="C14">
-        <v>138.29</v>
+        <v>136.7</v>
       </c>
       <c r="D14">
-        <v>30.05</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="15">
@@ -594,10 +594,10 @@
         <v>44152</v>
       </c>
       <c r="C15">
-        <v>159.16</v>
+        <v>156.76</v>
       </c>
       <c r="D15">
-        <v>20.56</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="16">
@@ -610,10 +610,10 @@
         <v>2871</v>
       </c>
       <c r="C16">
-        <v>203.57</v>
+        <v>201.35</v>
       </c>
       <c r="D16">
-        <v>5.79</v>
+        <v>6.85</v>
       </c>
     </row>
     <row r="17">
@@ -626,10 +626,10 @@
         <v>25005</v>
       </c>
       <c r="C17">
-        <v>132.31</v>
+        <v>130.58</v>
       </c>
       <c r="D17">
-        <v>29.73</v>
+        <v>31.16</v>
       </c>
     </row>
     <row r="18">
@@ -642,10 +642,10 @@
         <v>8776</v>
       </c>
       <c r="C18">
-        <v>119.93</v>
+        <v>118.1</v>
       </c>
       <c r="D18">
-        <v>36.72</v>
+        <v>38.59</v>
       </c>
     </row>
     <row r="19">
@@ -658,10 +658,10 @@
         <v>9939</v>
       </c>
       <c r="C19">
-        <v>215.19</v>
+        <v>213.26</v>
       </c>
       <c r="D19">
-        <v>3.86</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="20">
@@ -674,10 +674,10 @@
         <v>389</v>
       </c>
       <c r="C20">
-        <v>105.67</v>
+        <v>104.3</v>
       </c>
       <c r="D20">
-        <v>59.15</v>
+        <v>59.61</v>
       </c>
     </row>
     <row r="21">
@@ -690,10 +690,10 @@
         <v>1472</v>
       </c>
       <c r="C21">
-        <v>165.41</v>
+        <v>164.35</v>
       </c>
       <c r="D21">
-        <v>13.89</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="22">
@@ -706,10 +706,10 @@
         <v>160973</v>
       </c>
       <c r="C22">
-        <v>111.45</v>
+        <v>110.4</v>
       </c>
       <c r="D22">
-        <v>45.03</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="23">
@@ -722,10 +722,10 @@
         <v>278</v>
       </c>
       <c r="C23">
-        <v>101.37</v>
+        <v>99.95</v>
       </c>
       <c r="D23">
-        <v>66.34</v>
+        <v>66.64</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         <v>9376</v>
       </c>
       <c r="C24">
-        <v>131.86</v>
+        <v>130.24</v>
       </c>
       <c r="D24">
-        <v>40.38</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="25">
@@ -754,10 +754,10 @@
         <v>11339</v>
       </c>
       <c r="C25">
-        <v>174.21</v>
+        <v>171.66</v>
       </c>
       <c r="D25">
-        <v>6.99</v>
+        <v>9.15</v>
       </c>
     </row>
     <row r="26">
@@ -770,10 +770,10 @@
         <v>375</v>
       </c>
       <c r="C26">
-        <v>134.66</v>
+        <v>132.84</v>
       </c>
       <c r="D26">
-        <v>37.72</v>
+        <v>37.97</v>
       </c>
     </row>
     <row r="27">
@@ -786,10 +786,10 @@
         <v>12119</v>
       </c>
       <c r="C27">
-        <v>127.93</v>
+        <v>126.31</v>
       </c>
       <c r="D27">
-        <v>45.5</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="28">
@@ -802,10 +802,10 @@
         <v>753</v>
       </c>
       <c r="C28">
-        <v>123.31</v>
+        <v>122.26</v>
       </c>
       <c r="D28">
-        <v>47.65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -818,10 +818,10 @@
         <v>11338</v>
       </c>
       <c r="C29">
-        <v>109.27</v>
+        <v>107.72</v>
       </c>
       <c r="D29">
-        <v>59.75</v>
+        <v>60.04</v>
       </c>
     </row>
     <row r="30">
@@ -834,10 +834,10 @@
         <v>3338</v>
       </c>
       <c r="C30">
-        <v>141.66</v>
+        <v>139.75</v>
       </c>
       <c r="D30">
-        <v>24.97</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="31">
@@ -850,10 +850,10 @@
         <v>2258</v>
       </c>
       <c r="C31">
-        <v>186.51</v>
+        <v>184.64</v>
       </c>
       <c r="D31">
-        <v>9.09</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -866,10 +866,10 @@
         <v>203931</v>
       </c>
       <c r="C32">
-        <v>200.81</v>
+        <v>198.34</v>
       </c>
       <c r="D32">
-        <v>10.8</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="33">
@@ -882,10 +882,10 @@
         <v>434</v>
       </c>
       <c r="C33">
-        <v>144.34</v>
+        <v>143.13</v>
       </c>
       <c r="D33">
-        <v>22.54</v>
+        <v>22.86</v>
       </c>
     </row>
     <row r="34">
@@ -898,10 +898,10 @@
         <v>6938</v>
       </c>
       <c r="C34">
-        <v>96.09999999999999</v>
+        <v>94.76000000000001</v>
       </c>
       <c r="D34">
-        <v>62.86</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="35">
@@ -914,10 +914,10 @@
         <v>20003</v>
       </c>
       <c r="C35">
-        <v>221.74</v>
+        <v>219.04</v>
       </c>
       <c r="D35">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="36">
@@ -930,10 +930,10 @@
         <v>11642</v>
       </c>
       <c r="C36">
-        <v>118.57</v>
+        <v>117.09</v>
       </c>
       <c r="D36">
-        <v>37.73</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="37">
@@ -946,10 +946,10 @@
         <v>16004</v>
       </c>
       <c r="C37">
-        <v>165.24</v>
+        <v>163.6</v>
       </c>
       <c r="D37">
-        <v>12.74</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="38">
@@ -962,10 +962,10 @@
         <v>24278</v>
       </c>
       <c r="C38">
-        <v>177.97</v>
+        <v>175.74</v>
       </c>
       <c r="D38">
-        <v>6.67</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="39">
@@ -978,10 +978,10 @@
         <v>37171</v>
       </c>
       <c r="C39">
-        <v>153.67</v>
+        <v>151.66</v>
       </c>
       <c r="D39">
-        <v>21.68</v>
+        <v>23</v>
       </c>
     </row>
     <row r="40">
@@ -994,10 +994,10 @@
         <v>504</v>
       </c>
       <c r="C40">
-        <v>158.13</v>
+        <v>156.59</v>
       </c>
       <c r="D40">
-        <v>9.84</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="41">
@@ -1010,10 +1010,10 @@
         <v>4728</v>
       </c>
       <c r="C41">
-        <v>187.59</v>
+        <v>185.18</v>
       </c>
       <c r="D41">
-        <v>3.68</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="42">
@@ -1026,10 +1026,10 @@
         <v>15756</v>
       </c>
       <c r="C42">
-        <v>124.62</v>
+        <v>122.96</v>
       </c>
       <c r="D42">
-        <v>47.17</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="43">
@@ -1042,10 +1042,10 @@
         <v>18840</v>
       </c>
       <c r="C43">
-        <v>148.81</v>
+        <v>146.74</v>
       </c>
       <c r="D43">
-        <v>20.21</v>
+        <v>22.04</v>
       </c>
     </row>
     <row r="44">
@@ -1058,10 +1058,10 @@
         <v>1406343</v>
       </c>
       <c r="C44">
-        <v>151.67</v>
+        <v>150.12</v>
       </c>
       <c r="D44">
-        <v>28.16</v>
+        <v>28.77</v>
       </c>
     </row>
     <row r="45">
@@ -1074,10 +1074,10 @@
         <v>48792</v>
       </c>
       <c r="C45">
-        <v>96.77</v>
+        <v>95.66</v>
       </c>
       <c r="D45">
-        <v>70.06999999999999</v>
+        <v>70.09999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -1090,10 +1090,10 @@
         <v>756</v>
       </c>
       <c r="C46">
-        <v>135.81</v>
+        <v>134.2</v>
       </c>
       <c r="D46">
-        <v>26.01</v>
+        <v>26.42</v>
       </c>
     </row>
     <row r="47">
@@ -1106,10 +1106,10 @@
         <v>5376</v>
       </c>
       <c r="C47">
-        <v>172.36</v>
+        <v>170.36</v>
       </c>
       <c r="D47">
-        <v>8.17</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -1122,10 +1122,10 @@
         <v>87795</v>
       </c>
       <c r="C48">
-        <v>74.81</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="D48">
-        <v>84.95</v>
+        <v>86.68000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -1138,10 +1138,10 @@
         <v>4913</v>
       </c>
       <c r="C49">
-        <v>131.69</v>
+        <v>129.97</v>
       </c>
       <c r="D49">
-        <v>37.71</v>
+        <v>38.43</v>
       </c>
     </row>
     <row r="50">
@@ -1154,10 +1154,10 @@
         <v>3968</v>
       </c>
       <c r="C50">
-        <v>144.71</v>
+        <v>142.61</v>
       </c>
       <c r="D50">
-        <v>24.94</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="51">
@@ -1170,10 +1170,10 @@
         <v>11104</v>
       </c>
       <c r="C51">
-        <v>172.71</v>
+        <v>170.21</v>
       </c>
       <c r="D51">
-        <v>18.27</v>
+        <v>19.31</v>
       </c>
     </row>
     <row r="52">
@@ -1186,10 +1186,10 @@
         <v>1265</v>
       </c>
       <c r="C52">
-        <v>119.14</v>
+        <v>117.84</v>
       </c>
       <c r="D52">
-        <v>36.7</v>
+        <v>37.64</v>
       </c>
     </row>
     <row r="53">
@@ -1202,10 +1202,10 @@
         <v>10439</v>
       </c>
       <c r="C53">
-        <v>85.34999999999999</v>
+        <v>84.25</v>
       </c>
       <c r="D53">
-        <v>73.28</v>
+        <v>73.31</v>
       </c>
     </row>
     <row r="54">
@@ -1218,10 +1218,10 @@
         <v>26907</v>
       </c>
       <c r="C54">
-        <v>167.83</v>
+        <v>165.75</v>
       </c>
       <c r="D54">
-        <v>9.31</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="55">
@@ -1234,10 +1234,10 @@
         <v>5745</v>
       </c>
       <c r="C55">
-        <v>159.41</v>
+        <v>157.14</v>
       </c>
       <c r="D55">
-        <v>10.78</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="56">
@@ -1250,10 +1250,10 @@
         <v>1057</v>
       </c>
       <c r="C56">
-        <v>195.31</v>
+        <v>193.47</v>
       </c>
       <c r="D56">
-        <v>3.02</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="57">
@@ -1266,10 +1266,10 @@
         <v>67</v>
       </c>
       <c r="C57">
-        <v>105.66</v>
+        <v>104.21</v>
       </c>
       <c r="D57">
-        <v>61.13</v>
+        <v>61.5</v>
       </c>
     </row>
     <row r="58">
@@ -1282,10 +1282,10 @@
         <v>10631</v>
       </c>
       <c r="C58">
-        <v>148.38</v>
+        <v>146.38</v>
       </c>
       <c r="D58">
-        <v>30.69</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="59">
@@ -1298,10 +1298,10 @@
         <v>16910</v>
       </c>
       <c r="C59">
-        <v>47.84</v>
+        <v>47.23</v>
       </c>
       <c r="D59">
-        <v>94.09</v>
+        <v>94.73999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1314,10 +1314,10 @@
         <v>104191</v>
       </c>
       <c r="C60">
-        <v>147.62</v>
+        <v>146.05</v>
       </c>
       <c r="D60">
-        <v>16.41</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="61">
@@ -1330,10 +1330,10 @@
         <v>6120</v>
       </c>
       <c r="C61">
-        <v>156.61</v>
+        <v>154.52</v>
       </c>
       <c r="D61">
-        <v>24.49</v>
+        <v>25.12</v>
       </c>
     </row>
     <row r="62">
@@ -1346,10 +1346,10 @@
         <v>1593</v>
       </c>
       <c r="C62">
-        <v>131.14</v>
+        <v>129.64</v>
       </c>
       <c r="D62">
-        <v>29.63</v>
+        <v>29.95</v>
       </c>
     </row>
     <row r="63">
@@ -1362,10 +1362,10 @@
         <v>3128</v>
       </c>
       <c r="C63">
-        <v>156.07</v>
+        <v>154.35</v>
       </c>
       <c r="D63">
-        <v>11.01</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="64">
@@ -1378,10 +1378,10 @@
         <v>1310</v>
       </c>
       <c r="C64">
-        <v>126.66</v>
+        <v>124.76</v>
       </c>
       <c r="D64">
-        <v>36.6</v>
+        <v>38.09</v>
       </c>
     </row>
     <row r="65">
@@ -1394,10 +1394,10 @@
         <v>1145</v>
       </c>
       <c r="C65">
-        <v>78.64</v>
+        <v>77.83</v>
       </c>
       <c r="D65">
-        <v>81.20999999999999</v>
+        <v>82.01000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1410,10 +1410,10 @@
         <v>110537</v>
       </c>
       <c r="C66">
-        <v>173</v>
+        <v>171.15</v>
       </c>
       <c r="D66">
-        <v>9.27</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1426,10 +1426,10 @@
         <v>899</v>
       </c>
       <c r="C67">
-        <v>110.08</v>
+        <v>108.93</v>
       </c>
       <c r="D67">
-        <v>56.29</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="68">
@@ -1442,10 +1442,10 @@
         <v>5471</v>
       </c>
       <c r="C68">
-        <v>143.65</v>
+        <v>141.5</v>
       </c>
       <c r="D68">
-        <v>26.78</v>
+        <v>28.45</v>
       </c>
     </row>
     <row r="69">
@@ -1458,10 +1458,10 @@
         <v>64964</v>
       </c>
       <c r="C69">
-        <v>177.01</v>
+        <v>174.42</v>
       </c>
       <c r="D69">
-        <v>14.56</v>
+        <v>16.54</v>
       </c>
     </row>
     <row r="70">
@@ -1474,10 +1474,10 @@
         <v>2174</v>
       </c>
       <c r="C70">
-        <v>111.2</v>
+        <v>109.89</v>
       </c>
       <c r="D70">
-        <v>54.43</v>
+        <v>54.87</v>
       </c>
     </row>
     <row r="71">
@@ -1490,10 +1490,10 @@
         <v>2353</v>
       </c>
       <c r="C71">
-        <v>69.17</v>
+        <v>68.36</v>
       </c>
       <c r="D71">
-        <v>90.09</v>
+        <v>91.68000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -1506,10 +1506,10 @@
         <v>3743</v>
       </c>
       <c r="C72">
-        <v>177.19</v>
+        <v>174.78</v>
       </c>
       <c r="D72">
-        <v>17.85</v>
+        <v>19.08</v>
       </c>
     </row>
     <row r="73">
@@ -1522,10 +1522,10 @@
         <v>82695</v>
       </c>
       <c r="C73">
-        <v>159.62</v>
+        <v>156.83</v>
       </c>
       <c r="D73">
-        <v>7.97</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="74">
@@ -1538,10 +1538,10 @@
         <v>30106</v>
       </c>
       <c r="C74">
-        <v>177.59</v>
+        <v>175.59</v>
       </c>
       <c r="D74">
-        <v>4.26</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="75">
@@ -1554,10 +1554,10 @@
         <v>10634</v>
       </c>
       <c r="C75">
-        <v>160.11</v>
+        <v>157.42</v>
       </c>
       <c r="D75">
-        <v>8.19</v>
+        <v>11.92</v>
       </c>
     </row>
     <row r="76">
@@ -1570,10 +1570,10 @@
         <v>114</v>
       </c>
       <c r="C76">
-        <v>93.47</v>
+        <v>92.2</v>
       </c>
       <c r="D76">
-        <v>68.11</v>
+        <v>68.53</v>
       </c>
     </row>
     <row r="77">
@@ -1586,10 +1586,10 @@
         <v>16578</v>
       </c>
       <c r="C77">
-        <v>120.32</v>
+        <v>118.6</v>
       </c>
       <c r="D77">
-        <v>54.04</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="78">
@@ -1602,10 +1602,10 @@
         <v>12430</v>
       </c>
       <c r="C78">
-        <v>147.27</v>
+        <v>145.47</v>
       </c>
       <c r="D78">
-        <v>37.41</v>
+        <v>37.8</v>
       </c>
     </row>
     <row r="79">
@@ -1618,10 +1618,10 @@
         <v>1885</v>
       </c>
       <c r="C79">
-        <v>71.92</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="D79">
-        <v>88.06999999999999</v>
+        <v>89.58</v>
       </c>
     </row>
     <row r="80">
@@ -1634,10 +1634,10 @@
         <v>795</v>
       </c>
       <c r="C80">
-        <v>180.02</v>
+        <v>177.59</v>
       </c>
       <c r="D80">
-        <v>16.25</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="81">
@@ -1650,10 +1650,10 @@
         <v>10780</v>
       </c>
       <c r="C81">
-        <v>128.33</v>
+        <v>126.6</v>
       </c>
       <c r="D81">
-        <v>46.78</v>
+        <v>47.01</v>
       </c>
     </row>
     <row r="82">
@@ -1666,10 +1666,10 @@
         <v>9629</v>
       </c>
       <c r="C82">
-        <v>129.66</v>
+        <v>127.92</v>
       </c>
       <c r="D82">
-        <v>49.99</v>
+        <v>50.21</v>
       </c>
     </row>
     <row r="83">
@@ -1682,10 +1682,10 @@
         <v>9679</v>
       </c>
       <c r="C83">
-        <v>100.39</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="D83">
-        <v>61.1</v>
+        <v>61.8</v>
       </c>
     </row>
     <row r="84">
@@ -1698,10 +1698,10 @@
         <v>353</v>
       </c>
       <c r="C84">
-        <v>172.78</v>
+        <v>170.77</v>
       </c>
       <c r="D84">
-        <v>5.21</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="85">
@@ -1714,10 +1714,10 @@
         <v>1358101</v>
       </c>
       <c r="C85">
-        <v>104.69</v>
+        <v>103.74</v>
       </c>
       <c r="D85">
-        <v>52.8</v>
+        <v>52.86</v>
       </c>
     </row>
     <row r="86">
@@ -1730,10 +1730,10 @@
         <v>266686</v>
       </c>
       <c r="C86">
-        <v>173.78</v>
+        <v>172.16</v>
       </c>
       <c r="D86">
-        <v>9.35</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="87">
@@ -1746,10 +1746,10 @@
         <v>85202</v>
       </c>
       <c r="C87">
-        <v>126.72</v>
+        <v>125.55</v>
       </c>
       <c r="D87">
-        <v>38.87</v>
+        <v>39.35</v>
       </c>
     </row>
     <row r="88">
@@ -1762,10 +1762,10 @@
         <v>39650</v>
       </c>
       <c r="C88">
-        <v>147.61</v>
+        <v>145.96</v>
       </c>
       <c r="D88">
-        <v>18.78</v>
+        <v>19.19</v>
       </c>
     </row>
     <row r="89">
@@ -1778,10 +1778,10 @@
         <v>4843</v>
       </c>
       <c r="C89">
-        <v>142.44</v>
+        <v>140.73</v>
       </c>
       <c r="D89">
-        <v>22.48</v>
+        <v>23.85</v>
       </c>
     </row>
     <row r="90">
@@ -1794,10 +1794,10 @@
         <v>8408</v>
       </c>
       <c r="C90">
-        <v>158.36</v>
+        <v>156.28</v>
       </c>
       <c r="D90">
-        <v>24.76</v>
+        <v>25.53</v>
       </c>
     </row>
     <row r="91">
@@ -1810,10 +1810,10 @@
         <v>59785</v>
       </c>
       <c r="C91">
-        <v>162.45</v>
+        <v>159.72</v>
       </c>
       <c r="D91">
-        <v>12.85</v>
+        <v>15.75</v>
       </c>
     </row>
     <row r="92">
@@ -1826,10 +1826,10 @@
         <v>2788</v>
       </c>
       <c r="C92">
-        <v>176.21</v>
+        <v>174.37</v>
       </c>
       <c r="D92">
-        <v>11.97</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="93">
@@ -1842,10 +1842,10 @@
         <v>125913</v>
       </c>
       <c r="C93">
-        <v>113.57</v>
+        <v>111.19</v>
       </c>
       <c r="D93">
-        <v>44.97</v>
+        <v>47.64</v>
       </c>
     </row>
     <row r="94">
@@ -1858,10 +1858,10 @@
         <v>10346</v>
       </c>
       <c r="C94">
-        <v>151.98</v>
+        <v>150.53</v>
       </c>
       <c r="D94">
-        <v>15.47</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="95">
@@ -1874,10 +1874,10 @@
         <v>18657</v>
       </c>
       <c r="C95">
-        <v>196.79</v>
+        <v>194.58</v>
       </c>
       <c r="D95">
-        <v>6.98</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="96">
@@ -1890,10 +1890,10 @@
         <v>49286</v>
       </c>
       <c r="C96">
-        <v>110.28</v>
+        <v>109.08</v>
       </c>
       <c r="D96">
-        <v>54.33</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="97">
@@ -1906,10 +1906,10 @@
         <v>120</v>
       </c>
       <c r="C97">
-        <v>152.55</v>
+        <v>150.65</v>
       </c>
       <c r="D97">
-        <v>21.68</v>
+        <v>21.94</v>
       </c>
     </row>
     <row r="98">
@@ -1922,10 +1922,10 @@
         <v>4365</v>
       </c>
       <c r="C98">
-        <v>101.8</v>
+        <v>101.14</v>
       </c>
       <c r="D98">
-        <v>58.92</v>
+        <v>59.14</v>
       </c>
     </row>
     <row r="99">
@@ -1938,10 +1938,10 @@
         <v>6241</v>
       </c>
       <c r="C99">
-        <v>163.48</v>
+        <v>161.74</v>
       </c>
       <c r="D99">
-        <v>18.63</v>
+        <v>18.95</v>
       </c>
     </row>
     <row r="100">
@@ -1954,10 +1954,10 @@
         <v>7020</v>
       </c>
       <c r="C100">
-        <v>275.34</v>
+        <v>272.62</v>
       </c>
       <c r="D100">
-        <v>0.51</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="101">
@@ -1970,10 +1970,10 @@
         <v>1901</v>
       </c>
       <c r="C101">
-        <v>135.48</v>
+        <v>133.36</v>
       </c>
       <c r="D101">
-        <v>33.02</v>
+        <v>34.66</v>
       </c>
     </row>
     <row r="102">
@@ -1986,10 +1986,10 @@
         <v>5797</v>
       </c>
       <c r="C102">
-        <v>232.63</v>
+        <v>230.15</v>
       </c>
       <c r="D102">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="103">
@@ -2002,10 +2002,10 @@
         <v>2140</v>
       </c>
       <c r="C103">
-        <v>112.79</v>
+        <v>111.56</v>
       </c>
       <c r="D103">
-        <v>44.67</v>
+        <v>45.01</v>
       </c>
     </row>
     <row r="104">
@@ -2018,10 +2018,10 @@
         <v>4838</v>
       </c>
       <c r="C104">
-        <v>131.94</v>
+        <v>130.43</v>
       </c>
       <c r="D104">
-        <v>26.47</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="105">
@@ -2034,10 +2034,10 @@
         <v>6768</v>
       </c>
       <c r="C105">
-        <v>104.34</v>
+        <v>103.34</v>
       </c>
       <c r="D105">
-        <v>57.84</v>
+        <v>58.21</v>
       </c>
     </row>
     <row r="106">
@@ -2050,10 +2050,10 @@
         <v>2767</v>
       </c>
       <c r="C106">
-        <v>162.64</v>
+        <v>160.16</v>
       </c>
       <c r="D106">
-        <v>17.15</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="107">
@@ -2066,10 +2066,10 @@
         <v>608</v>
       </c>
       <c r="C107">
-        <v>161.74</v>
+        <v>159.83</v>
       </c>
       <c r="D107">
-        <v>8.15</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="108">
@@ -2082,10 +2082,10 @@
         <v>26962</v>
       </c>
       <c r="C108">
-        <v>56.66</v>
+        <v>56.04</v>
       </c>
       <c r="D108">
-        <v>98.51000000000001</v>
+        <v>99.09</v>
       </c>
     </row>
     <row r="109">
@@ -2098,10 +2098,10 @@
         <v>18176</v>
       </c>
       <c r="C109">
-        <v>184.95</v>
+        <v>182.79</v>
       </c>
       <c r="D109">
-        <v>3.29</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="110">
@@ -2114,10 +2114,10 @@
         <v>32675</v>
       </c>
       <c r="C110">
-        <v>128.79</v>
+        <v>127.59</v>
       </c>
       <c r="D110">
-        <v>33</v>
+        <v>33.31</v>
       </c>
     </row>
     <row r="111">
@@ -2130,10 +2130,10 @@
         <v>474</v>
       </c>
       <c r="C111">
-        <v>178.46</v>
+        <v>177.08</v>
       </c>
       <c r="D111">
-        <v>7.76</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="112">
@@ -2146,10 +2146,10 @@
         <v>19932</v>
       </c>
       <c r="C112">
-        <v>181.1</v>
+        <v>178.66</v>
       </c>
       <c r="D112">
-        <v>6.38</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="113">
@@ -2162,10 +2162,10 @@
         <v>489</v>
       </c>
       <c r="C113">
-        <v>155.6</v>
+        <v>153.68</v>
       </c>
       <c r="D113">
-        <v>20.59</v>
+        <v>21.88</v>
       </c>
     </row>
     <row r="114">
@@ -2178,10 +2178,10 @@
         <v>44</v>
       </c>
       <c r="C114">
-        <v>167.08</v>
+        <v>165.44</v>
       </c>
       <c r="D114">
-        <v>14.64</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="115">
@@ -2194,10 +2194,10 @@
         <v>4248</v>
       </c>
       <c r="C115">
-        <v>155.27</v>
+        <v>153.21</v>
       </c>
       <c r="D115">
-        <v>12.58</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="116">
@@ -2210,10 +2210,10 @@
         <v>1275</v>
       </c>
       <c r="C116">
-        <v>135.82</v>
+        <v>134.65</v>
       </c>
       <c r="D116">
-        <v>18.86</v>
+        <v>19.71</v>
       </c>
     </row>
     <row r="117">
@@ -2226,10 +2226,10 @@
         <v>123071</v>
       </c>
       <c r="C117">
-        <v>152.36</v>
+        <v>150.35</v>
       </c>
       <c r="D117">
-        <v>33.4</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="118">
@@ -2242,10 +2242,10 @@
         <v>108</v>
       </c>
       <c r="C118">
-        <v>129.63</v>
+        <v>128.22</v>
       </c>
       <c r="D118">
-        <v>33.21</v>
+        <v>33.36</v>
       </c>
     </row>
     <row r="119">
@@ -2258,10 +2258,10 @@
         <v>3094</v>
       </c>
       <c r="C119">
-        <v>71.28</v>
+        <v>70.47</v>
       </c>
       <c r="D119">
-        <v>85.7</v>
+        <v>85.94</v>
       </c>
     </row>
     <row r="120">
@@ -2274,10 +2274,10 @@
         <v>3126</v>
       </c>
       <c r="C120">
-        <v>195.1</v>
+        <v>192.91</v>
       </c>
       <c r="D120">
-        <v>7.48</v>
+        <v>7.88</v>
       </c>
     </row>
     <row r="121">
@@ -2290,10 +2290,10 @@
         <v>606</v>
       </c>
       <c r="C121">
-        <v>244.65</v>
+        <v>241.49</v>
       </c>
       <c r="D121">
-        <v>1.2</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="122">
@@ -2306,10 +2306,10 @@
         <v>35374</v>
       </c>
       <c r="C122">
-        <v>166.09</v>
+        <v>164.62</v>
       </c>
       <c r="D122">
-        <v>21.72</v>
+        <v>22.09</v>
       </c>
     </row>
     <row r="123">
@@ -2322,10 +2322,10 @@
         <v>28350</v>
       </c>
       <c r="C123">
-        <v>113.17</v>
+        <v>111.74</v>
       </c>
       <c r="D123">
-        <v>52.89</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="124">
@@ -2338,10 +2338,10 @@
         <v>51544</v>
       </c>
       <c r="C124">
-        <v>184.55</v>
+        <v>182.93</v>
       </c>
       <c r="D124">
-        <v>25.96</v>
+        <v>26.23</v>
       </c>
     </row>
     <row r="125">
@@ -2354,10 +2354,10 @@
         <v>2536</v>
       </c>
       <c r="C125">
-        <v>125.02</v>
+        <v>123.6</v>
       </c>
       <c r="D125">
-        <v>33.79</v>
+        <v>34.13</v>
       </c>
     </row>
     <row r="126">
@@ -2370,10 +2370,10 @@
         <v>27554</v>
       </c>
       <c r="C126">
-        <v>136.83</v>
+        <v>135.44</v>
       </c>
       <c r="D126">
-        <v>20.66</v>
+        <v>21.11</v>
       </c>
     </row>
     <row r="127">
@@ -2386,10 +2386,10 @@
         <v>17302</v>
       </c>
       <c r="C127">
-        <v>164.55</v>
+        <v>162.31</v>
       </c>
       <c r="D127">
-        <v>9.33</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="128">
@@ -2402,10 +2402,10 @@
         <v>4883</v>
       </c>
       <c r="C128">
-        <v>177.81</v>
+        <v>175.54</v>
       </c>
       <c r="D128">
-        <v>6.45</v>
+        <v>7.63</v>
       </c>
     </row>
     <row r="129">
@@ -2418,10 +2418,10 @@
         <v>6308</v>
       </c>
       <c r="C129">
-        <v>139.59</v>
+        <v>137.7</v>
       </c>
       <c r="D129">
-        <v>35.82</v>
+        <v>36.18</v>
       </c>
     </row>
     <row r="130">
@@ -2434,10 +2434,10 @@
         <v>21638</v>
       </c>
       <c r="C130">
-        <v>205.17</v>
+        <v>202.47</v>
       </c>
       <c r="D130">
-        <v>2.92</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="131">
@@ -2450,10 +2450,10 @@
         <v>200330</v>
       </c>
       <c r="C131">
-        <v>117.62</v>
+        <v>116.22</v>
       </c>
       <c r="D131">
-        <v>50.78</v>
+        <v>51.22</v>
       </c>
     </row>
     <row r="132">
@@ -2466,10 +2466,10 @@
         <v>1888</v>
       </c>
       <c r="C132">
-        <v>169.42</v>
+        <v>167.49</v>
       </c>
       <c r="D132">
-        <v>11.13</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="133">
@@ -2482,10 +2482,10 @@
         <v>5273</v>
       </c>
       <c r="C133">
-        <v>175.58</v>
+        <v>173.3</v>
       </c>
       <c r="D133">
-        <v>13.45</v>
+        <v>14.75</v>
       </c>
     </row>
     <row r="134">
@@ -2498,10 +2498,10 @@
         <v>4528</v>
       </c>
       <c r="C134">
-        <v>151.97</v>
+        <v>150.78</v>
       </c>
       <c r="D134">
-        <v>9.609999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="135">
@@ -2514,10 +2514,10 @@
         <v>222488</v>
       </c>
       <c r="C135">
-        <v>100.05</v>
+        <v>98.87</v>
       </c>
       <c r="D135">
-        <v>59.8</v>
+        <v>59.88</v>
       </c>
     </row>
     <row r="136">
@@ -2530,7 +2530,7 @@
         <v>4759</v>
       </c>
       <c r="C136">
-        <v>532.72</v>
+        <v>526</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2546,10 +2546,10 @@
         <v>4126</v>
       </c>
       <c r="C137">
-        <v>158.85</v>
+        <v>156.61</v>
       </c>
       <c r="D137">
-        <v>24.42</v>
+        <v>25.11</v>
       </c>
     </row>
     <row r="138">
@@ -2562,10 +2562,10 @@
         <v>9256</v>
       </c>
       <c r="C138">
-        <v>126.46</v>
+        <v>125.08</v>
       </c>
       <c r="D138">
-        <v>35.34</v>
+        <v>35.51</v>
       </c>
     </row>
     <row r="139">
@@ -2578,10 +2578,10 @@
         <v>6333</v>
       </c>
       <c r="C139">
-        <v>177.69</v>
+        <v>175.15</v>
       </c>
       <c r="D139">
-        <v>19.72</v>
+        <v>20.12</v>
       </c>
     </row>
     <row r="140">
@@ -2594,10 +2594,10 @@
         <v>31699</v>
       </c>
       <c r="C140">
-        <v>163.69</v>
+        <v>161.46</v>
       </c>
       <c r="D140">
-        <v>23</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="141">
@@ -2610,10 +2610,10 @@
         <v>107874</v>
       </c>
       <c r="C141">
-        <v>183.65</v>
+        <v>181.92</v>
       </c>
       <c r="D141">
-        <v>26.34</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="142">
@@ -2626,10 +2626,10 @@
         <v>37855</v>
       </c>
       <c r="C142">
-        <v>149.3</v>
+        <v>147.59</v>
       </c>
       <c r="D142">
-        <v>25.83</v>
+        <v>26.88</v>
       </c>
     </row>
     <row r="143">
@@ -2642,10 +2642,10 @@
         <v>10237</v>
       </c>
       <c r="C143">
-        <v>165.47</v>
+        <v>162.84</v>
       </c>
       <c r="D143">
-        <v>11.59</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="144">
@@ -2658,10 +2658,10 @@
         <v>2752</v>
       </c>
       <c r="C144">
-        <v>146.57</v>
+        <v>145.94</v>
       </c>
       <c r="D144">
-        <v>10.18</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="145">
@@ -2674,10 +2674,10 @@
         <v>19349</v>
       </c>
       <c r="C145">
-        <v>155.61</v>
+        <v>153.57</v>
       </c>
       <c r="D145">
-        <v>21.71</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="146">
@@ -2690,10 +2690,10 @@
         <v>144900</v>
       </c>
       <c r="C146">
-        <v>142.15</v>
+        <v>140.43</v>
       </c>
       <c r="D146">
-        <v>25.19</v>
+        <v>26.57</v>
       </c>
     </row>
     <row r="147">
@@ -2706,10 +2706,10 @@
         <v>12256</v>
       </c>
       <c r="C147">
-        <v>152.99</v>
+        <v>151.31</v>
       </c>
       <c r="D147">
-        <v>34.26</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="148">
@@ -2722,10 +2722,10 @@
         <v>203</v>
       </c>
       <c r="C148">
-        <v>177.83</v>
+        <v>175.3</v>
       </c>
       <c r="D148">
-        <v>17.51</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="149">
@@ -2738,10 +2738,10 @@
         <v>29560</v>
       </c>
       <c r="C149">
-        <v>199.13</v>
+        <v>197.6</v>
       </c>
       <c r="D149">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="150">
@@ -2754,10 +2754,10 @@
         <v>15639</v>
       </c>
       <c r="C150">
-        <v>133.46</v>
+        <v>131.91</v>
       </c>
       <c r="D150">
-        <v>43</v>
+        <v>43.4</v>
       </c>
     </row>
     <row r="151">
@@ -2770,10 +2770,10 @@
         <v>6928</v>
       </c>
       <c r="C151">
-        <v>185.7</v>
+        <v>183.12</v>
       </c>
       <c r="D151">
-        <v>12.61</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="152">
@@ -2786,10 +2786,10 @@
         <v>115</v>
       </c>
       <c r="C152">
-        <v>107.28</v>
+        <v>106.26</v>
       </c>
       <c r="D152">
-        <v>48.73</v>
+        <v>49.25</v>
       </c>
     </row>
     <row r="153">
@@ -2802,10 +2802,10 @@
         <v>7405</v>
       </c>
       <c r="C153">
-        <v>175.05</v>
+        <v>173.12</v>
       </c>
       <c r="D153">
-        <v>4.95</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="154">
@@ -2818,10 +2818,10 @@
         <v>5611</v>
       </c>
       <c r="C154">
-        <v>157.99</v>
+        <v>156.72</v>
       </c>
       <c r="D154">
-        <v>15.47</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="155">
@@ -2834,10 +2834,10 @@
         <v>5388</v>
       </c>
       <c r="C155">
-        <v>95.28</v>
+        <v>94.22</v>
       </c>
       <c r="D155">
-        <v>63.21</v>
+        <v>63.3</v>
       </c>
     </row>
     <row r="156">
@@ -2850,10 +2850,10 @@
         <v>2057</v>
       </c>
       <c r="C156">
-        <v>121.12</v>
+        <v>119.36</v>
       </c>
       <c r="D156">
-        <v>41.21</v>
+        <v>42.61</v>
       </c>
     </row>
     <row r="157">
@@ -2866,10 +2866,10 @@
         <v>700</v>
       </c>
       <c r="C157">
-        <v>173.62</v>
+        <v>171.4</v>
       </c>
       <c r="D157">
-        <v>16.01</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="158">
@@ -2882,10 +2882,10 @@
         <v>57950</v>
       </c>
       <c r="C158">
-        <v>166.93</v>
+        <v>165.26</v>
       </c>
       <c r="D158">
-        <v>4.78</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="159">
@@ -2898,10 +2898,10 @@
         <v>51388</v>
       </c>
       <c r="C159">
-        <v>140.03</v>
+        <v>138.48</v>
       </c>
       <c r="D159">
-        <v>33.05</v>
+        <v>33.96</v>
       </c>
     </row>
     <row r="160">
@@ -2914,10 +2914,10 @@
         <v>10007</v>
       </c>
       <c r="C160">
-        <v>142.11</v>
+        <v>140.57</v>
       </c>
       <c r="D160">
-        <v>21.5</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="161">
@@ -2930,10 +2930,10 @@
         <v>46862</v>
       </c>
       <c r="C161">
-        <v>144.52</v>
+        <v>142.4</v>
       </c>
       <c r="D161">
-        <v>18.71</v>
+        <v>21.12</v>
       </c>
     </row>
     <row r="162">
@@ -2946,10 +2946,10 @@
         <v>21998</v>
       </c>
       <c r="C162">
-        <v>123.52</v>
+        <v>122.26</v>
       </c>
       <c r="D162">
-        <v>48.43</v>
+        <v>48.89</v>
       </c>
     </row>
     <row r="163">
@@ -2962,10 +2962,10 @@
         <v>175</v>
       </c>
       <c r="C163">
-        <v>73.36</v>
+        <v>72.53</v>
       </c>
       <c r="D163">
-        <v>87.48999999999999</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="164">
@@ -2978,10 +2978,10 @@
         <v>103</v>
       </c>
       <c r="C164">
-        <v>152.65</v>
+        <v>150.49</v>
       </c>
       <c r="D164">
-        <v>23.01</v>
+        <v>24.18</v>
       </c>
     </row>
     <row r="165">
@@ -2994,10 +2994,10 @@
         <v>43422</v>
       </c>
       <c r="C165">
-        <v>155.79</v>
+        <v>153.95</v>
       </c>
       <c r="D165">
-        <v>10.87</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="166">
@@ -3010,10 +3010,10 @@
         <v>592</v>
       </c>
       <c r="C166">
-        <v>131.46</v>
+        <v>129.7</v>
       </c>
       <c r="D166">
-        <v>39.86</v>
+        <v>40.16</v>
       </c>
     </row>
     <row r="167">
@@ -3026,10 +3026,10 @@
         <v>10114</v>
       </c>
       <c r="C167">
-        <v>126.29</v>
+        <v>124.34</v>
       </c>
       <c r="D167">
-        <v>31.38</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="168">
@@ -3042,10 +3042,10 @@
         <v>8460</v>
       </c>
       <c r="C168">
-        <v>112.78</v>
+        <v>111.17</v>
       </c>
       <c r="D168">
-        <v>44.52</v>
+        <v>45.59</v>
       </c>
     </row>
     <row r="169">
@@ -3058,10 +3058,10 @@
         <v>19584</v>
       </c>
       <c r="C169">
-        <v>126.54</v>
+        <v>125.44</v>
       </c>
       <c r="D169">
-        <v>39.6</v>
+        <v>39.97</v>
       </c>
     </row>
     <row r="170">
@@ -3074,10 +3074,10 @@
         <v>206</v>
       </c>
       <c r="C170">
-        <v>111.71</v>
+        <v>110.36</v>
       </c>
       <c r="D170">
-        <v>54.03</v>
+        <v>54.49</v>
       </c>
     </row>
     <row r="171">
@@ -3090,10 +3090,10 @@
         <v>23498</v>
       </c>
       <c r="C171">
-        <v>140.12</v>
+        <v>138.58</v>
       </c>
       <c r="D171">
-        <v>21.64</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="172">
@@ -3106,10 +3106,10 @@
         <v>9151</v>
       </c>
       <c r="C172">
-        <v>171.21</v>
+        <v>169.25</v>
       </c>
       <c r="D172">
-        <v>13.14</v>
+        <v>13.37</v>
       </c>
     </row>
     <row r="173">
@@ -3122,10 +3122,10 @@
         <v>56218</v>
       </c>
       <c r="C173">
-        <v>109.2</v>
+        <v>107.85</v>
       </c>
       <c r="D173">
-        <v>44.77</v>
+        <v>45.11</v>
       </c>
     </row>
     <row r="174">
@@ -3138,10 +3138,10 @@
         <v>70794</v>
       </c>
       <c r="C174">
-        <v>83.15000000000001</v>
+        <v>82.34</v>
       </c>
       <c r="D174">
-        <v>78.08</v>
+        <v>78.12</v>
       </c>
     </row>
     <row r="175">
@@ -3154,10 +3154,10 @@
         <v>1255</v>
       </c>
       <c r="C175">
-        <v>221.56</v>
+        <v>219.19</v>
       </c>
       <c r="D175">
-        <v>0.6899999999999999</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="176">
@@ -3170,10 +3170,10 @@
         <v>8095</v>
       </c>
       <c r="C176">
-        <v>155.02</v>
+        <v>153.23</v>
       </c>
       <c r="D176">
-        <v>14.11</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="177">
@@ -3186,10 +3186,10 @@
         <v>103</v>
       </c>
       <c r="C177">
-        <v>129.45</v>
+        <v>127.65</v>
       </c>
       <c r="D177">
-        <v>42.58</v>
+        <v>42.98</v>
       </c>
     </row>
     <row r="178">
@@ -3202,10 +3202,10 @@
         <v>1474</v>
       </c>
       <c r="C178">
-        <v>60.26</v>
+        <v>59.6</v>
       </c>
       <c r="D178">
-        <v>91.23999999999999</v>
+        <v>91.26000000000001</v>
       </c>
     </row>
     <row r="179">
@@ -3218,10 +3218,10 @@
         <v>11620</v>
       </c>
       <c r="C179">
-        <v>166.41</v>
+        <v>164.75</v>
       </c>
       <c r="D179">
-        <v>9.81</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="180">
@@ -3234,10 +3234,10 @@
         <v>83603</v>
       </c>
       <c r="C180">
-        <v>147.05</v>
+        <v>145.6</v>
       </c>
       <c r="D180">
-        <v>17.97</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="181">
@@ -3250,10 +3250,10 @@
         <v>6563</v>
       </c>
       <c r="C181">
-        <v>151.86</v>
+        <v>150.25</v>
       </c>
       <c r="D181">
-        <v>21.47</v>
+        <v>21.67</v>
       </c>
     </row>
     <row r="182">
@@ -3266,10 +3266,10 @@
         <v>40741</v>
       </c>
       <c r="C182">
-        <v>132.64</v>
+        <v>131.01</v>
       </c>
       <c r="D182">
-        <v>26.69</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="183">
@@ -3282,10 +3282,10 @@
         <v>44714</v>
       </c>
       <c r="C183">
-        <v>101.23</v>
+        <v>99.97</v>
       </c>
       <c r="D183">
-        <v>57.76</v>
+        <v>58.02</v>
       </c>
     </row>
     <row r="184">
@@ -3298,10 +3298,10 @@
         <v>9297</v>
       </c>
       <c r="C184">
-        <v>126.48</v>
+        <v>125.88</v>
       </c>
       <c r="D184">
-        <v>30.13</v>
+        <v>30.21</v>
       </c>
     </row>
     <row r="185">
@@ -3314,10 +3314,10 @@
         <v>66201</v>
       </c>
       <c r="C185">
-        <v>119.94</v>
+        <v>118.18</v>
       </c>
       <c r="D185">
-        <v>38.63</v>
+        <v>40.15</v>
       </c>
     </row>
     <row r="186">
@@ -3330,10 +3330,10 @@
         <v>332631</v>
       </c>
       <c r="C186">
-        <v>139.84</v>
+        <v>138.08</v>
       </c>
       <c r="D186">
-        <v>26.64</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="187">
@@ -3346,10 +3346,10 @@
         <v>3357</v>
       </c>
       <c r="C187">
-        <v>177.19</v>
+        <v>174.3</v>
       </c>
       <c r="D187">
-        <v>13.11</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="188">
@@ -3362,10 +3362,10 @@
         <v>31893</v>
       </c>
       <c r="C188">
-        <v>200.59</v>
+        <v>198.45</v>
       </c>
       <c r="D188">
-        <v>10.55</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="189">
@@ -3378,10 +3378,10 @@
         <v>280</v>
       </c>
       <c r="C189">
-        <v>208.58</v>
+        <v>205.79</v>
       </c>
       <c r="D189">
-        <v>3.14</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="190">
@@ -3394,10 +3394,10 @@
         <v>28801</v>
       </c>
       <c r="C190">
-        <v>118.69</v>
+        <v>117.09</v>
       </c>
       <c r="D190">
-        <v>50.88</v>
+        <v>51.14</v>
       </c>
     </row>
     <row r="191">
@@ -3410,10 +3410,10 @@
         <v>95272</v>
       </c>
       <c r="C191">
-        <v>185.34</v>
+        <v>183.58</v>
       </c>
       <c r="D191">
-        <v>5.09</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="192">
@@ -3426,10 +3426,10 @@
         <v>33392</v>
       </c>
       <c r="C192">
-        <v>159.83</v>
+        <v>158.07</v>
       </c>
       <c r="D192">
-        <v>11.23</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="193">
@@ -3442,10 +3442,10 @@
         <v>17625</v>
       </c>
       <c r="C193">
-        <v>138.67</v>
+        <v>137.05</v>
       </c>
       <c r="D193">
-        <v>20.22</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="194">
@@ -3458,10 +3458,10 @@
         <v>14694</v>
       </c>
       <c r="C194">
-        <v>109.23</v>
+        <v>107.95</v>
       </c>
       <c r="D194">
-        <v>47.64</v>
+        <v>47.94</v>
       </c>
     </row>
   </sheetData>
